--- a/templates/ordem-de-compra.xlsx
+++ b/templates/ordem-de-compra.xlsx
@@ -26,8 +26,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Familia!$B$2:$D$2</definedName>
     <definedName name="BARUERI">Familia!$F$3:$F$5</definedName>
     <definedName name="DadosExternos_2" localSheetId="3" hidden="1">'Fornecedores '!$A$1:$O$89</definedName>
-    <definedName name="DadosExternos_3" localSheetId="2" hidden="1">Produtos!$A$1:$L$1048528</definedName>
-    <definedName name="Distribuidor">'[1]ORDEM DE COMPRA'!$U$9:$U$1048576</definedName>
     <definedName name="Distribuidores" localSheetId="0">'Ordem de Compra'!#REF!</definedName>
     <definedName name="Distribuidores">#REF!</definedName>
     <definedName name="ES">Familia!$D$3:$D$16</definedName>
@@ -11716,37 +11714,6 @@
 </queryTable>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D87D1BF4-D53B-40A1-A380-6AF02994E8E6}" name="Produtos__2" displayName="Produtos__2" ref="A1:L1048528" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:L1048528" xr:uid="{D87D1BF4-D53B-40A1-A380-6AF02994E8E6}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Fone blindado modelo bd306-1"/>
-        <filter val="Fone blindado para modelo - TC320-1"/>
-        <filter val="Fone ouv Poly VOY 5200 USB-A BTHS+BT700"/>
-        <filter val="MICROFONE - CISCO TABLE MICROPHONE PRO (W/11M CABLE), CARBON BLACK-SPARE"/>
-        <filter val="TELEFONE CISCO IP 7821COM FONTE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0BD7196E-6D08-4A12-958C-C5A8E5F7C700}" uniqueName="1" name="PART NUMBER - Coluna 1" queryTableFieldId="1" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{2425C3CB-4F1E-4D81-9DB1-DA6FDA6024DA}" uniqueName="2" name="DESCRIÇÃO - Coluna 2" queryTableFieldId="2" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{12EC6124-D380-4046-88AF-8134391E9095}" uniqueName="3" name="LOCAL DO ESTOQUE - Coluna 3" queryTableFieldId="3" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{3A52A97A-96BC-406D-A5DD-462AC8D7453A}" uniqueName="4" name="CFOP - Coluna 4" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{24D89398-F3D5-49EE-A363-A2E71494F3CA}" uniqueName="5" name="NATUREZA - Coluna 5" queryTableFieldId="5" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{32B1D7D8-A137-4785-BBE9-903A010B02D6}" uniqueName="6" name="FAMÍLIA - Coluna 6" queryTableFieldId="6" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{EA6D41F6-BDAE-4160-B469-FD5C47F720DF}" uniqueName="7" name="NCM - Coluna 7" queryTableFieldId="7" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{174B2ADB-2822-443C-B161-19E401287C9E}" uniqueName="8" name="ATÉ            15 " queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{AF8C14E4-6102-4795-AE24-D17B1801F9F8}" uniqueName="9" name="ATÉ            120" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{E7660C87-45B7-44FF-8F92-67A7D7907059}" uniqueName="10" name="Column10" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{CD7C1924-4BA4-4C72-88E0-145380545766}" uniqueName="11" name="Column11" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{0F213BBA-BABB-4210-A429-37234D6C8953}" uniqueName="12" name="Column12" queryTableFieldId="12"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A87A2144-CBD5-4690-BE54-8B8D1AC174AF}" name="Fornecedores" displayName="Fornecedores" ref="A1:O89" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:O89" xr:uid="{A87A2144-CBD5-4690-BE54-8B8D1AC174AF}"/>
